--- a/data/50001569 - EUROHINCA.xlsx
+++ b/data/50001569 - EUROHINCA.xlsx
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46212.8959703125</v>
+        <v>46213.90764578704</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>184</v>

--- a/data/50001569 - EUROHINCA.xlsx
+++ b/data/50001569 - EUROHINCA.xlsx
@@ -3256,7 +3256,7 @@
         <v>46209.792292743055</v>
       </c>
       <c r="D27" s="9">
-        <v>46212.64675210648</v>
+        <v>46214.18292518519</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>92</v>
@@ -3303,8 +3303,8 @@
       <c r="S27" s="10">
         <v>1</v>
       </c>
-      <c r="T27" s="7" t="s">
-        <v>53</v>
+      <c r="T27" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U27" s="12" t="s">
         <v>94</v>

--- a/data/50001569 - EUROHINCA.xlsx
+++ b/data/50001569 - EUROHINCA.xlsx
@@ -479,7 +479,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386</t>
+    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc ot 4385- 4386,Generacion Oc OT 4376 OT 4381  </t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3546,7 +3546,7 @@
         <v>46237.55370259259</v>
       </c>
       <c r="D31" s="9">
-        <v>46237.55371959491</v>
+        <v>46237.570408472224</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>108</v>
